--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:25</t>
+    <t xml:space="preserve">2026-09-10 01:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:40</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-23 15:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernandez</t>
+    <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:41</t>
+    <t xml:space="preserve">2026-10-04 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:49</t>
+    <t xml:space="preserve">2026-10-05 16:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1324,7 +1324,7 @@
         <v>106.85</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>57.12</v>
+        <v>57.13</v>
       </c>
     </row>
     <row r="28">
